--- a/dcf/KVYO.xlsx
+++ b/dcf/KVYO.xlsx
@@ -194,8 +194,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -431,7 +431,7 @@
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>User-edited — overridden from Opus 12.0x</t>
+        <t>User-edited — overridden from Opus 12.0x on 2026-07-07</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
@@ -848,7 +848,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1130,25 +1130,25 @@
         <v>12.8</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>20.91566321761408</v>
+        <v>17.9156502347187</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>20.170412292729</v>
+        <v>17.30196490238792</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>19.46098333395037</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>18.78547095126732</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>18.1420800042282</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>17.52911873037271</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>16.94499233180684</v>
+        <v>16.71766456260655</v>
+      </c>
+      <c r="E5" s="54" t="n">
+        <v>16.16118890080211</v>
+      </c>
+      <c r="F5" s="54" t="n">
+        <v>15.6310678025272</v>
+      </c>
+      <c r="G5" s="54" t="n">
+        <v>15.12591573457542</v>
+      </c>
+      <c r="H5" s="54" t="n">
+        <v>14.64442650059042</v>
       </c>
     </row>
     <row r="6">
@@ -1156,25 +1156,25 @@
         <v>13.8</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>21.9424992111121</v>
+        <v>18.7540839368797</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>21.15016688392232</v>
+        <v>18.10195562564361</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>20.39602024740207</v>
+        <v>17.48114233896677</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>19.67802504251781</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>18.99426483661554</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>18.34293367427561</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>17.72232921841766</v>
+        <v>16.88997853794442</v>
+      </c>
+      <c r="F6" s="54" t="n">
+        <v>16.32689507043388</v>
+      </c>
+      <c r="G6" s="54" t="n">
+        <v>15.7904131622182</v>
+      </c>
+      <c r="H6" s="54" t="n">
+        <v>15.27913880887948</v>
       </c>
     </row>
     <row r="7">
@@ -1182,25 +1182,25 @@
         <v>14.8</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>22.96933520461012</v>
+        <v>19.5925176390407</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>22.12992147511565</v>
+        <v>18.90194634889929</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>21.33105716085378</v>
+        <v>18.244620115327</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>20.5705791337683</v>
+        <v>17.61876817508674</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>19.84644966900288</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>19.15674861817851</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>18.49966610502848</v>
+        <v>17.02272233834056</v>
+      </c>
+      <c r="G7" s="54" t="n">
+        <v>16.45491058986099</v>
+      </c>
+      <c r="H7" s="54" t="n">
+        <v>15.91385111716853</v>
       </c>
     </row>
     <row r="8">
@@ -1208,25 +1208,25 @@
         <v>15.8</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>23.99617119810815</v>
+        <v>20.4309513412017</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>23.10967606630897</v>
+        <v>19.70193707215498</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>22.26609407430549</v>
-      </c>
-      <c r="E8" s="54" t="n">
-        <v>21.46313322501879</v>
+        <v>19.00809789168722</v>
+      </c>
+      <c r="E8" s="55" t="n">
+        <v>18.34755781222906</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>20.69863450139022</v>
+        <v>17.71854960624724</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>19.97056356208142</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>19.2770029916393</v>
+        <v>17.11940801750377</v>
+      </c>
+      <c r="H8" s="54" t="n">
+        <v>16.54856342545759</v>
       </c>
     </row>
     <row r="9">
@@ -1234,25 +1234,25 @@
         <v>16.8</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>25.02300719160617</v>
+        <v>21.2693850433627</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>24.08943065750229</v>
+        <v>20.50192779541067</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>23.2011309877572</v>
+        <v>19.77157566804744</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>22.35568731626928</v>
+        <v>19.07634744937137</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>21.55081933377756</v>
+        <v>18.41437687415392</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>20.78437850598432</v>
+        <v>17.78390544514655</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>20.05433987825013</v>
+        <v>17.18327573374664</v>
       </c>
     </row>
     <row r="10">
@@ -1260,25 +1260,25 @@
         <v>17.8</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>26.04984318510419</v>
+        <v>22.10781874552369</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>25.06918524869562</v>
+        <v>21.30191851866635</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>24.13616790120891</v>
+        <v>20.53505344440766</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>23.24824140751976</v>
+        <v>19.80513708651369</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>22.4030041661649</v>
+        <v>19.11020414206059</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>21.59819344988722</v>
+        <v>18.44840287278933</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>20.83167676486095</v>
+        <v>17.8179880420357</v>
       </c>
     </row>
     <row r="11">
@@ -1286,25 +1286,25 @@
         <v>18.8</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>27.07667917860222</v>
+        <v>22.9462524476847</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>26.04893983988894</v>
+        <v>22.10190924192204</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>25.07120481466062</v>
+        <v>21.29853122076789</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>24.14079549877025</v>
+        <v>20.533926723656</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>23.25518899855224</v>
+        <v>19.80603140996727</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>22.41200839379012</v>
+        <v>19.11290030043211</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>21.60901365147177</v>
+        <v>18.45270035032476</v>
       </c>
     </row>
     <row r="13">
@@ -1313,7 +1313,7 @@
           <t>Current price</t>
         </is>
       </c>
-      <c r="B13" s="55" t="n">
+      <c r="B13" s="54" t="n">
         <v>16.64520072937012</v>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.7558144323936011</v>
+        <v>0.7696489512164543</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24419,7 +24419,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24571,13 +24571,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>21.46313322501879</v>
+        <v>18.34755781222906</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>30.37415909917886</v>
+        <v>25.22836434365009</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>15.02183977668893</v>
+        <v>13.23372504715624</v>
       </c>
     </row>
     <row r="59">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="F20" s="31" t="inlineStr">
         <is>
-          <t>overridden from Opus 12.0x</t>
+          <t>overridden from Opus 12.0x on 2026-07-07</t>
         </is>
       </c>
     </row>
